--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -39679,6 +39679,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1710">
+      <c r="A1710" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1710" t="n">
+        <v>1750</v>
+      </c>
+      <c r="C1710" t="n">
+        <v>3.65000009536743</v>
+      </c>
+      <c r="D1710" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="E1710" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="F1710" t="n">
+        <v>3.65000009536743</v>
+      </c>
+      <c r="G1710" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -39702,6 +39702,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1711">
+      <c r="A1711" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1711" t="n">
+        <v>750</v>
+      </c>
+      <c r="C1711" t="n">
+        <v>3.72000002861023</v>
+      </c>
+      <c r="D1711" t="n">
+        <v>3.70000004768372</v>
+      </c>
+      <c r="E1711" t="n">
+        <v>3.70000004768372</v>
+      </c>
+      <c r="F1711" t="n">
+        <v>3.72000002861023</v>
+      </c>
+      <c r="G1711" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -39725,6 +39725,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1712">
+      <c r="A1712" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1712" t="n">
+        <v>3250</v>
+      </c>
+      <c r="C1712" t="n">
+        <v>3.78999996185303</v>
+      </c>
+      <c r="D1712" t="n">
+        <v>3.70000004768372</v>
+      </c>
+      <c r="E1712" t="n">
+        <v>3.73000001907349</v>
+      </c>
+      <c r="F1712" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="G1712" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -39748,6 +39748,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1713">
+      <c r="A1713" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1713" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1713" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="D1713" t="n">
+        <v>3.80999994277954</v>
+      </c>
+      <c r="E1713" t="n">
+        <v>3.80999994277954</v>
+      </c>
+      <c r="F1713" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="G1713" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -39589,22 +39589,22 @@
     </row>
     <row r="1706">
       <c r="A1706" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1706" t="n">
-        <v>1750</v>
+        <v>4750</v>
       </c>
       <c r="C1706" t="n">
-        <v>3.6800000667572</v>
+        <v>3.61999988555908</v>
       </c>
       <c r="D1706" t="n">
-        <v>3.58999991416931</v>
+        <v>3.52999997138977</v>
       </c>
       <c r="E1706" t="n">
-        <v>3.67000007629395</v>
+        <v>3.60999989509583</v>
       </c>
       <c r="F1706" t="n">
-        <v>3.58999991416931</v>
+        <v>3.61999988555908</v>
       </c>
       <c r="G1706" t="s">
         <v>7</v>
@@ -39612,22 +39612,22 @@
     </row>
     <row r="1707">
       <c r="A1707" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1707" t="n">
-        <v>1500</v>
+        <v>1750</v>
       </c>
       <c r="C1707" t="n">
-        <v>3.65000009536743</v>
+        <v>3.6800000667572</v>
       </c>
       <c r="D1707" t="n">
-        <v>3.55999994277954</v>
+        <v>3.58999991416931</v>
       </c>
       <c r="E1707" t="n">
-        <v>3.65000009536743</v>
+        <v>3.67000007629395</v>
       </c>
       <c r="F1707" t="n">
-        <v>3.55999994277954</v>
+        <v>3.58999991416931</v>
       </c>
       <c r="G1707" t="s">
         <v>7</v>
@@ -39635,19 +39635,19 @@
     </row>
     <row r="1708">
       <c r="A1708" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1708" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="C1708" t="n">
-        <v>3.55999994277954</v>
+        <v>3.65000009536743</v>
       </c>
       <c r="D1708" t="n">
         <v>3.55999994277954</v>
       </c>
       <c r="E1708" t="n">
-        <v>3.55999994277954</v>
+        <v>3.65000009536743</v>
       </c>
       <c r="F1708" t="n">
         <v>3.55999994277954</v>
@@ -39658,22 +39658,22 @@
     </row>
     <row r="1709">
       <c r="A1709" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1709" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="C1709" t="n">
-        <v>3.65000009536743</v>
+        <v>3.55999994277954</v>
       </c>
       <c r="D1709" t="n">
-        <v>3.35999989509583</v>
+        <v>3.55999994277954</v>
       </c>
       <c r="E1709" t="n">
-        <v>3.49000000953674</v>
+        <v>3.55999994277954</v>
       </c>
       <c r="F1709" t="n">
-        <v>3.52999997138977</v>
+        <v>3.55999994277954</v>
       </c>
       <c r="G1709" t="s">
         <v>7</v>
@@ -39681,22 +39681,22 @@
     </row>
     <row r="1710">
       <c r="A1710" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1710" t="n">
-        <v>1750</v>
+        <v>4500</v>
       </c>
       <c r="C1710" t="n">
         <v>3.65000009536743</v>
       </c>
       <c r="D1710" t="n">
-        <v>3.57999992370605</v>
+        <v>3.35999989509583</v>
       </c>
       <c r="E1710" t="n">
-        <v>3.57999992370605</v>
+        <v>3.49000000953674</v>
       </c>
       <c r="F1710" t="n">
-        <v>3.65000009536743</v>
+        <v>3.52999997138977</v>
       </c>
       <c r="G1710" t="s">
         <v>7</v>
@@ -39704,22 +39704,22 @@
     </row>
     <row r="1711">
       <c r="A1711" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1711" t="n">
-        <v>750</v>
+        <v>1750</v>
       </c>
       <c r="C1711" t="n">
-        <v>3.72000002861023</v>
+        <v>3.65000009536743</v>
       </c>
       <c r="D1711" t="n">
-        <v>3.70000004768372</v>
+        <v>3.57999992370605</v>
       </c>
       <c r="E1711" t="n">
-        <v>3.70000004768372</v>
+        <v>3.57999992370605</v>
       </c>
       <c r="F1711" t="n">
-        <v>3.72000002861023</v>
+        <v>3.65000009536743</v>
       </c>
       <c r="G1711" t="s">
         <v>7</v>
@@ -39727,22 +39727,22 @@
     </row>
     <row r="1712">
       <c r="A1712" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1712" t="n">
-        <v>3250</v>
+        <v>750</v>
       </c>
       <c r="C1712" t="n">
-        <v>3.78999996185303</v>
+        <v>3.72000002861023</v>
       </c>
       <c r="D1712" t="n">
         <v>3.70000004768372</v>
       </c>
       <c r="E1712" t="n">
-        <v>3.73000001907349</v>
+        <v>3.70000004768372</v>
       </c>
       <c r="F1712" t="n">
-        <v>3.74000000953674</v>
+        <v>3.72000002861023</v>
       </c>
       <c r="G1712" t="s">
         <v>7</v>
@@ -39750,24 +39750,47 @@
     </row>
     <row r="1713">
       <c r="A1713" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1713" t="n">
-        <v>1000</v>
+        <v>3250</v>
       </c>
       <c r="C1713" t="n">
-        <v>3.83999991416931</v>
+        <v>3.78999996185303</v>
       </c>
       <c r="D1713" t="n">
-        <v>3.80999994277954</v>
+        <v>3.70000004768372</v>
       </c>
       <c r="E1713" t="n">
-        <v>3.80999994277954</v>
+        <v>3.73000001907349</v>
       </c>
       <c r="F1713" t="n">
-        <v>3.83999991416931</v>
+        <v>3.74000000953674</v>
       </c>
       <c r="G1713" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1714" t="n">
+        <v>14500</v>
+      </c>
+      <c r="C1714" t="n">
+        <v>4.07000017166138</v>
+      </c>
+      <c r="D1714" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="E1714" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="F1714" t="n">
+        <v>3.84999990463257</v>
+      </c>
+      <c r="G1714" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -44991,6 +44991,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1717">
+      <c r="A1717" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1717" t="n">
+        <v>9250</v>
+      </c>
+      <c r="C1717" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="D1717" t="n">
+        <v>3.94000005722046</v>
+      </c>
+      <c r="E1717" t="n">
+        <v>3.94000005722046</v>
+      </c>
+      <c r="F1717" t="n">
+        <v>3.97000002861023</v>
+      </c>
+      <c r="G1717" t="n">
+        <v>3.97000002861023</v>
+      </c>
+      <c r="H1717" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -45017,6 +45017,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1718">
+      <c r="A1718" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1718" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C1718" t="n">
+        <v>4.05999994277954</v>
+      </c>
+      <c r="D1718" t="n">
+        <v>3.84999990463257</v>
+      </c>
+      <c r="E1718" t="n">
+        <v>4.05999994277954</v>
+      </c>
+      <c r="F1718" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G1718" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="H1718" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -45043,6 +45043,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1719">
+      <c r="A1719" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1719" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C1719" t="n">
+        <v>3.97000002861023</v>
+      </c>
+      <c r="D1719" t="n">
+        <v>3.84999990463257</v>
+      </c>
+      <c r="E1719" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F1719" t="n">
+        <v>3.84999990463257</v>
+      </c>
+      <c r="G1719" t="n">
+        <v>3.84999990463257</v>
+      </c>
+      <c r="H1719" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -45069,6 +45069,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1720">
+      <c r="A1720" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1720" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1720" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="D1720" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E1720" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="F1720" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="G1720" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="H1720" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -45147,6 +45147,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1723">
+      <c r="A1723" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1723" t="n">
+        <v>1250</v>
+      </c>
+      <c r="C1723" t="n">
+        <v>4.05000019073486</v>
+      </c>
+      <c r="D1723" t="n">
+        <v>4.01999998092651</v>
+      </c>
+      <c r="E1723" t="n">
+        <v>4.01999998092651</v>
+      </c>
+      <c r="F1723" t="n">
+        <v>4.05000019073486</v>
+      </c>
+      <c r="G1723" t="n">
+        <v>4.05000019073486</v>
+      </c>
+      <c r="H1723" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -40058,13 +40058,36 @@
         <v>3.99000000953674</v>
       </c>
       <c r="D1726" t="n">
-        <v>3.92000007629395</v>
+        <v>3.86999988555908</v>
       </c>
       <c r="E1726" t="n">
         <v>3.98000001907349</v>
       </c>
-      <c r="F1726"/>
+      <c r="F1726" t="n">
+        <v>3.86999988555908</v>
+      </c>
       <c r="G1726" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1727" t="n">
+        <v>500</v>
+      </c>
+      <c r="C1727" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="D1727" t="n">
+        <v>3.80999994277954</v>
+      </c>
+      <c r="E1727" t="n">
+        <v>3.80999994277954</v>
+      </c>
+      <c r="F1727"/>
+      <c r="G1727" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -40086,8 +40086,31 @@
       <c r="E1727" t="n">
         <v>3.80999994277954</v>
       </c>
-      <c r="F1727"/>
+      <c r="F1727" t="n">
+        <v>3.9300000667572</v>
+      </c>
       <c r="G1727" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1728" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C1728" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D1728" t="n">
+        <v>3.85999989509583</v>
+      </c>
+      <c r="E1728" t="n">
+        <v>3.86999988555908</v>
+      </c>
+      <c r="F1728"/>
+      <c r="G1728" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -40109,8 +40109,31 @@
       <c r="E1728" t="n">
         <v>3.86999988555908</v>
       </c>
-      <c r="F1728"/>
+      <c r="F1728" t="n">
+        <v>3.90000009536743</v>
+      </c>
       <c r="G1728" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1729" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C1729" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D1729" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="E1729" t="n">
+        <v>3.80999994277954</v>
+      </c>
+      <c r="F1729"/>
+      <c r="G1729" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -40132,8 +40132,31 @@
       <c r="E1729" t="n">
         <v>3.80999994277954</v>
       </c>
-      <c r="F1729"/>
+      <c r="F1729" t="n">
+        <v>3.82999992370605</v>
+      </c>
       <c r="G1729" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1730" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C1730" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="D1730" t="n">
+        <v>3.86999988555908</v>
+      </c>
+      <c r="E1730" t="n">
+        <v>3.86999988555908</v>
+      </c>
+      <c r="F1730"/>
+      <c r="G1730" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -40162,6 +40162,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1731">
+      <c r="A1731" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1731" t="n">
+        <v>250</v>
+      </c>
+      <c r="C1731" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D1731" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E1731" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F1731" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G1731" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -45433,6 +45433,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1734">
+      <c r="A1734" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1734" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1734" t="n">
+        <v>3.78999996185303</v>
+      </c>
+      <c r="D1734" t="n">
+        <v>3.65000009536743</v>
+      </c>
+      <c r="E1734" t="n">
+        <v>3.67000007629395</v>
+      </c>
+      <c r="F1734" t="n">
+        <v>3.70000004768372</v>
+      </c>
+      <c r="G1734" t="n">
+        <v>3.70000004768372</v>
+      </c>
+      <c r="H1734" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -45459,6 +45459,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1735">
+      <c r="A1735" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1735" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C1735" t="n">
+        <v>3.65000009536743</v>
+      </c>
+      <c r="D1735" t="n">
+        <v>3.4300000667572</v>
+      </c>
+      <c r="E1735" t="n">
+        <v>3.4300000667572</v>
+      </c>
+      <c r="F1735" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="G1735" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="H1735" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -50722,6 +50722,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1737">
+      <c r="A1737" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1737" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1737" t="n">
+        <v>3.46000003814697</v>
+      </c>
+      <c r="D1737" t="n">
+        <v>3.46000003814697</v>
+      </c>
+      <c r="E1737" t="n">
+        <v>3.16000008583069</v>
+      </c>
+      <c r="F1737" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="G1737" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="H1737" t="n">
+        <v>22000</v>
+      </c>
+      <c r="I1737" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -50751,6 +50751,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1738">
+      <c r="A1738" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1738" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1738" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="D1738" t="n">
+        <v>3.3199999332428</v>
+      </c>
+      <c r="E1738" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="F1738" t="n">
+        <v>3.3199999332428</v>
+      </c>
+      <c r="G1738" t="n">
+        <v>3.3199999332428</v>
+      </c>
+      <c r="H1738" t="n">
+        <v>1250</v>
+      </c>
+      <c r="I1738" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -50780,6 +50780,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1739">
+      <c r="A1739" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1739" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1739" t="n">
+        <v>3.35999989509583</v>
+      </c>
+      <c r="D1739" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E1739" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="F1739" t="n">
+        <v>3.36999988555908</v>
+      </c>
+      <c r="G1739" t="n">
+        <v>3.36999988555908</v>
+      </c>
+      <c r="H1739" t="n">
+        <v>9250</v>
+      </c>
+      <c r="I1739" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -50809,6 +50809,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1740">
+      <c r="A1740" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1740" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1740" t="n">
+        <v>3.28999996185303</v>
+      </c>
+      <c r="D1740" t="n">
+        <v>3.28999996185303</v>
+      </c>
+      <c r="E1740" t="n">
+        <v>3.21000003814697</v>
+      </c>
+      <c r="F1740" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="G1740" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="H1740" t="n">
+        <v>6250</v>
+      </c>
+      <c r="I1740" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -50820,7 +50820,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="D1740" t="n">
-        <v>3.28999996185303</v>
+        <v>3.29999995231628</v>
       </c>
       <c r="E1740" t="n">
         <v>3.21000003814697</v>
@@ -50835,6 +50835,35 @@
         <v>6250</v>
       </c>
       <c r="I1740" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1741" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1741" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="D1741" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="E1741" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="F1741" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="G1741" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="H1741" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I1741" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -50867,6 +50867,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1742">
+      <c r="A1742" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1742" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1742" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D1742" t="n">
+        <v>3.27999997138977</v>
+      </c>
+      <c r="E1742" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="F1742" t="n">
+        <v>3.27999997138977</v>
+      </c>
+      <c r="G1742" t="n">
+        <v>3.27999997138977</v>
+      </c>
+      <c r="H1742" t="n">
+        <v>4250</v>
+      </c>
+      <c r="I1742" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -50896,6 +50896,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1743">
+      <c r="A1743" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1743" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1743" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D1743" t="n">
+        <v>3.3199999332428</v>
+      </c>
+      <c r="E1743" t="n">
+        <v>3.21000003814697</v>
+      </c>
+      <c r="F1743" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G1743" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H1743" t="n">
+        <v>1750</v>
+      </c>
+      <c r="I1743" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -50925,6 +50925,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1744">
+      <c r="A1744" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1744" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1744" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="D1744" t="n">
+        <v>3.30999994277954</v>
+      </c>
+      <c r="E1744" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F1744" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="G1744" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="H1744" t="n">
+        <v>2750</v>
+      </c>
+      <c r="I1744" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DOX.MI.xlsx
+++ b/data/DOX.MI.xlsx
@@ -50954,6 +50954,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1745">
+      <c r="A1745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1745" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1745" t="n">
+        <v>3.34999990463257</v>
+      </c>
+      <c r="D1745" t="n">
+        <v>3.42000007629395</v>
+      </c>
+      <c r="E1745" t="n">
+        <v>3.34999990463257</v>
+      </c>
+      <c r="F1745" t="n">
+        <v>3.42000007629395</v>
+      </c>
+      <c r="G1745" t="n">
+        <v>3.42000007629395</v>
+      </c>
+      <c r="H1745" t="n">
+        <v>2250</v>
+      </c>
+      <c r="I1745" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
